--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487396_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487396_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5212</v>
+        <v>4.2247</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6547</v>
+        <v>2.3048</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8665</v>
+        <v>1.92</v>
       </c>
       <c r="G2" t="n">
         <v>2.1759</v>
@@ -610,13 +610,13 @@
         <v>1.3709</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3085</v>
+        <v>0.0121</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7705</v>
+        <v>0.4205</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4619</v>
+        <v>-0.4085</v>
       </c>
       <c r="V2" t="n">
         <v>0.6659</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Y. PINAS</t>
+          <t>Á. SONEIRA BOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6672</v>
+        <v>1.2108</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0083</v>
+        <v>-1.7852</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6755</v>
+        <v>2.996</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1878</v>
+        <v>0.6794</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0569</v>
+        <v>-0.5835</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1309</v>
+        <v>1.2629</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2804</v>
+        <v>-0.0955</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4016</v>
+        <v>-1.2012</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1212</v>
+        <v>1.1057</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0926</v>
+        <v>0.7749</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3448</v>
+        <v>0.6177</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2521</v>
+        <v>0.1572</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3917</v>
+        <v>1.1751</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.1336</v>
+        <v>-1.1751</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7419</v>
+        <v>2.3502</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4206</v>
+        <v>-0.6437</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5796</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.159</v>
+        <v>-0.1291</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8260999999999999</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8260999999999999</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1477</v>
+        <v>1.198</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3143</v>
+        <v>-0.0503</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4621</v>
+        <v>1.2482</v>
       </c>
       <c r="G4" t="n">
         <v>0.364</v>
@@ -766,13 +766,13 @@
         <v>0.9792</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1955</v>
+        <v>-0.1453</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5346</v>
+        <v>-0.2705</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3391</v>
+        <v>0.1253</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Á. SONEIRA BOO</t>
+          <t>Y. PINAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4839</v>
+        <v>1.1648</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.4586</v>
+        <v>-1.484</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9425</v>
+        <v>2.6488</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6794</v>
+        <v>-0.1878</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5835</v>
+        <v>-0.0569</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2629</v>
+        <v>-0.1309</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0955</v>
+        <v>-0.2804</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2012</v>
+        <v>-0.4016</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1057</v>
+        <v>0.1212</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7749</v>
+        <v>0.0926</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6177</v>
+        <v>0.3448</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1572</v>
+        <v>-0.2521</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1751</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1751</v>
+        <v>-3.1336</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3502</v>
+        <v>2.7419</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3706</v>
+        <v>0.9182</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.188</v>
+        <v>1.1039</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1826</v>
+        <v>-0.1857</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1942</v>
+        <v>0.3338</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4652</v>
+        <v>-1.4058</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6594</v>
+        <v>1.7396</v>
       </c>
       <c r="G6" t="n">
         <v>1.6707</v>
@@ -922,13 +922,13 @@
         <v>0.5875</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5341</v>
+        <v>-0.3945</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5346</v>
+        <v>-0.4752</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0005</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5507</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. MARTINEZ CARRO</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2943</v>
+        <v>0.1233</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0214</v>
+        <v>-2.0798</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3157</v>
+        <v>2.2032</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0546</v>
+        <v>1.3584</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4083</v>
+        <v>0.9187</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3537</v>
+        <v>0.4397</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0808</v>
+        <v>-0.2195</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.301</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0808</v>
+        <v>-0.5206</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1354</v>
+        <v>1.578</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4083</v>
+        <v>0.6177</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2729</v>
+        <v>0.9603</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1958</v>
+        <v>1.3709</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1958</v>
+        <v>2.3502</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1602</v>
+        <v>-1.1141</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0594</v>
+        <v>-0.881</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1008</v>
+        <v>-0.233</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2754</v>
+        <v>-1.492</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2754</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>T. MARTINEZ CARRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3292</v>
+        <v>-0.2408</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5056</v>
+        <v>0.0214</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1764</v>
+        <v>-0.2623</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3584</v>
+        <v>-0.0546</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9187</v>
+        <v>-0.4083</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4397</v>
+        <v>0.3537</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2195</v>
+        <v>0.0808</v>
       </c>
       <c r="K8" t="n">
-        <v>0.301</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5206</v>
+        <v>0.0808</v>
       </c>
       <c r="M8" t="n">
-        <v>1.578</v>
+        <v>-0.1354</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6177</v>
+        <v>-0.4083</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9603</v>
+        <v>0.2729</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3709</v>
+        <v>0.1958</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3502</v>
+        <v>0.1958</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5666</v>
+        <v>-0.1067</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3068</v>
+        <v>-0.0594</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2598</v>
+        <v>-0.0473</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.492</v>
+        <v>-0.2754</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.492</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-1.0033</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6565</v>
+        <v>-3.5971</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9413</v>
+        <v>2.5938</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9382</v>
@@ -1156,13 +1156,13 @@
         <v>2.7419</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7299</v>
+        <v>0.4418</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1206</v>
+        <v>-0.0612</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8505</v>
+        <v>0.503</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1152</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2549</v>
+        <v>-1.8899</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1141</v>
+        <v>-2.9094</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8592</v>
+        <v>1.0196</v>
       </c>
       <c r="G10" t="n">
         <v>0.131</v>
@@ -1234,13 +1234,13 @@
         <v>1.3709</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5818</v>
+        <v>-0.2167</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5346</v>
+        <v>-0.3299</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0472</v>
+        <v>0.1132</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2166</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1178</v>
+        <v>-2.5538</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3254</v>
+        <v>-3.0019</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2076</v>
+        <v>0.4482</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4729</v>
@@ -1312,13 +1312,13 @@
         <v>1.5668</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3535</v>
+        <v>-0.7894</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4464</v>
+        <v>-0.1229</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9071</v>
+        <v>-0.6665</v>
       </c>
       <c r="V11" t="n">
         <v>0.2754</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.5572</v>
+        <v>-8.228</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.2399</v>
+        <v>-5.8306</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3173</v>
+        <v>-2.3975</v>
       </c>
       <c r="G12" t="n">
         <v>-4.3874</v>
@@ -1390,13 +1390,13 @@
         <v>1.3709</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2493</v>
+        <v>0.0798</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3276</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.07829999999999999</v>
+        <v>-0.0019</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1578</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.2544</v>
+        <v>-5.660399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-20.4118</v>
+        <v>-19.8179</v>
       </c>
       <c r="F13" t="n">
-        <v>14.1575</v>
+        <v>14.1576</v>
       </c>
       <c r="G13" t="n">
         <v>0.3384999999999998</v>
@@ -1468,13 +1468,13 @@
         <v>17.6262</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.5526</v>
+        <v>-1.9585</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.702499999999999</v>
+        <v>-1.1086</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.85</v>
+        <v>-0.8498</v>
       </c>
       <c r="V13" t="n">
         <v>-4.0403</v>
@@ -1483,7 +1483,7 @@
         <v>1.8124</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.852699999999999</v>
+        <v>-5.8527</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0758</v>
+        <v>3.2224</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8927</v>
+        <v>1.1998</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1831</v>
+        <v>2.0227</v>
       </c>
       <c r="G14" t="n">
         <v>1.9773</v>
@@ -1546,13 +1546,13 @@
         <v>0.7834</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.2244</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3564</v>
+        <v>-0.0494</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4342</v>
+        <v>0.2738</v>
       </c>
       <c r="V14" t="n">
         <v>1.2166</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5435</v>
+        <v>2.8108</v>
       </c>
       <c r="E15" t="n">
         <v>-0.8386</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3821</v>
+        <v>3.6494</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5493</v>
@@ -1624,13 +1624,13 @@
         <v>2.3502</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1606</v>
+        <v>0.1067</v>
       </c>
       <c r="T15" t="n">
         <v>-0.2329</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0723</v>
+        <v>0.3397</v>
       </c>
       <c r="V15" t="n">
         <v>1.8825</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1516</v>
+        <v>2.7121</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.8493</v>
+        <v>-2.2353</v>
       </c>
       <c r="F16" t="n">
-        <v>5.0009</v>
+        <v>4.9474</v>
       </c>
       <c r="G16" t="n">
         <v>0.2021</v>
@@ -1702,13 +1702,13 @@
         <v>2.7419</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1073</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7193000000000001</v>
+        <v>-0.1053</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8266</v>
+        <v>0.7731</v>
       </c>
       <c r="V16" t="n">
         <v>0.2754</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. LAROUSSE</t>
+          <t>L. SANCHEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1111</v>
+        <v>1.3078</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8446</v>
+        <v>0.1042</v>
       </c>
       <c r="F17" t="n">
-        <v>3.9557</v>
+        <v>1.2036</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0271</v>
+        <v>0.4706</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8272</v>
+        <v>0.3341</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8542999999999999</v>
+        <v>0.1364</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3302</v>
+        <v>0.0612</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4918</v>
+        <v>0.0612</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1617</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3572</v>
+        <v>0.4093</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3354</v>
+        <v>0.2729</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6926</v>
+        <v>0.1364</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1336</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7419</v>
+        <v>0.1958</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8663</v>
+        <v>0.2508</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0096</v>
+        <v>0.0429</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8566</v>
+        <v>0.2079</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3905</v>
+        <v>0.3905</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3905</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. SANCHEZ VAZQUEZ</t>
+          <t>A. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2589</v>
+        <v>0.7247</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0018</v>
+        <v>0.0484</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2571</v>
+        <v>0.6763</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4706</v>
+        <v>2.3851</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3341</v>
+        <v>-1.672</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1364</v>
+        <v>4.0571</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0612</v>
+        <v>1.88</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0612</v>
+        <v>-1.2012</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.0812</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4093</v>
+        <v>0.5051</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2729</v>
+        <v>-0.4708</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1364</v>
+        <v>0.9759</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1958</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.1336</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1958</v>
+        <v>2.546</v>
       </c>
       <c r="S18" t="n">
-        <v>0.202</v>
+        <v>-0.1316</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0594</v>
+        <v>-0.19</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2614</v>
+        <v>0.0584</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3905</v>
+        <v>-0.9412</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3905</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. IGLESIAS FERNANDEZ</t>
+          <t>S. MARTINEZ GRANDA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6491</v>
+        <v>0.4755</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0539</v>
+        <v>-2.9809</v>
       </c>
       <c r="F19" t="n">
-        <v>0.703</v>
+        <v>3.4564</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3851</v>
+        <v>-1.2933</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.672</v>
+        <v>-1.0712</v>
       </c>
       <c r="I19" t="n">
-        <v>4.0571</v>
+        <v>-0.2221</v>
       </c>
       <c r="J19" t="n">
-        <v>1.88</v>
+        <v>-2.3296</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2012</v>
+        <v>-1.0055</v>
       </c>
       <c r="L19" t="n">
-        <v>3.0812</v>
+        <v>-1.3241</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5051</v>
+        <v>1.0363</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4708</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9759</v>
+        <v>1.102</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5875</v>
+        <v>0.1958</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1336</v>
+        <v>-2.1543</v>
       </c>
       <c r="R19" t="n">
-        <v>2.546</v>
+        <v>2.3502</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2072</v>
+        <v>0.6317</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2923</v>
+        <v>0.2864</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0851</v>
+        <v>0.3452</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9412</v>
+        <v>0.9412</v>
       </c>
       <c r="W19" t="n">
-        <v>1.492</v>
+        <v>1.2166</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4332</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. MARTINEZ GRANDA</t>
+          <t>C. LAROUSSE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.05</v>
+        <v>0.2774</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1856</v>
+        <v>-3.2773</v>
       </c>
       <c r="F20" t="n">
-        <v>3.1356</v>
+        <v>3.5548</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2933</v>
+        <v>0.0271</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0712</v>
+        <v>-0.8272</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2221</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.3296</v>
+        <v>-0.3302</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0055</v>
+        <v>-0.4918</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3241</v>
+        <v>0.1617</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0363</v>
+        <v>0.3572</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.3354</v>
       </c>
       <c r="O20" t="n">
-        <v>1.102</v>
+        <v>0.6926</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1958</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1543</v>
+        <v>-3.1336</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3502</v>
+        <v>2.7419</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1062</v>
+        <v>1.0326</v>
       </c>
       <c r="T20" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.577</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0245</v>
+        <v>0.4557</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9412</v>
+        <v>-0.3905</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2166</v>
+        <v>-0.3905</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3563</v>
+        <v>-0.383</v>
       </c>
       <c r="E21" t="n">
         <v>-1.2865</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9302</v>
+        <v>0.9034</v>
       </c>
       <c r="G21" t="n">
         <v>0.7554999999999999</v>
@@ -2092,13 +2092,13 @@
         <v>1.3709</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.249</v>
+        <v>-0.2757</v>
       </c>
       <c r="T21" t="n">
         <v>0.207</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.456</v>
+        <v>-0.4827</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2754</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9907</v>
+        <v>-1.5604</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3204</v>
+        <v>-1.7298</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3298</v>
+        <v>0.1694</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2399</v>
@@ -2170,13 +2170,13 @@
         <v>1.1751</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9911</v>
+        <v>0.4214</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9663</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0248</v>
+        <v>-0.1356</v>
       </c>
       <c r="V22" t="n">
         <v>1.2166</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1388</v>
+        <v>-3.3331</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6732</v>
+        <v>-3.1615</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4656</v>
+        <v>-0.1715</v>
       </c>
       <c r="G23" t="n">
         <v>-3.0738</v>
@@ -2248,13 +2248,13 @@
         <v>1.3709</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1814</v>
+        <v>-0.3757</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7546</v>
+        <v>-0.2429</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4268</v>
+        <v>-0.1328</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2754</v>
@@ -2284,19 +2284,19 @@
         <v>6.254200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-14.1576</v>
+        <v>-14.1575</v>
       </c>
       <c r="F24" t="n">
         <v>20.4119</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3385999999999996</v>
+        <v>-0.3386</v>
       </c>
       <c r="H24" t="n">
         <v>-3.0675</v>
       </c>
       <c r="I24" t="n">
-        <v>2.729000000000001</v>
+        <v>2.729</v>
       </c>
       <c r="J24" t="n">
         <v>-3.2337</v>
@@ -2314,10 +2314,10 @@
         <v>-1.3282</v>
       </c>
       <c r="O24" t="n">
-        <v>4.223199999999999</v>
+        <v>4.2232</v>
       </c>
       <c r="P24" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>-1.665334536937735e-16</v>
       </c>
       <c r="Q24" t="n">
         <v>-17.6263</v>
@@ -2326,10 +2326,10 @@
         <v>17.6263</v>
       </c>
       <c r="S24" t="n">
-        <v>2.552499999999999</v>
+        <v>2.5524</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8496999999999998</v>
+        <v>0.8497999999999998</v>
       </c>
       <c r="U24" t="n">
         <v>1.7027</v>
@@ -2341,7 +2341,7 @@
         <v>5.852799999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.8125</v>
+        <v>-1.812499999999999</v>
       </c>
     </row>
   </sheetData>
